--- a/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
@@ -628,10 +628,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -640,7 +640,7 @@
         <v>28</v>
       </c>
       <c r="G4">
-        <v>84.84999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -765,10 +765,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>31</v>
@@ -902,10 +902,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -914,7 +914,7 @@
         <v>28</v>
       </c>
       <c r="G4">
-        <v>84.84999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H4">
         <v>7.4</v>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
     <t>LOYO</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>LORENZO</t>
   </si>
   <si>
     <t>ARGÜELLO</t>
@@ -103,27 +109,27 @@
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>RICO</t>
   </si>
   <si>
     <t>ROSETE</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>NARANJO</t>
   </si>
   <si>
@@ -145,16 +151,25 @@
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
+    <t>ROBERTO</t>
   </si>
   <si>
     <t>ATZIN HEFZIBA</t>
@@ -172,13 +187,13 @@
     <t>YAEL</t>
   </si>
   <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
     <t>DIEGO HUMBERTO</t>
   </si>
   <si>
     <t>ZURIEL ELIHU</t>
+  </si>
+  <si>
+    <t>DARINKA</t>
   </si>
 </sst>
 </file>
@@ -579,16 +594,16 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>76.67</v>
+        <v>80</v>
       </c>
       <c r="H2">
         <v>6.5</v>
@@ -722,16 +737,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>5.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -745,16 +763,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <v>36</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -791,16 +812,19 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
         <v>20</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>74.06999999999999</v>
+      </c>
+      <c r="H5">
+        <v>5.4</v>
       </c>
     </row>
   </sheetData>
@@ -853,19 +877,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>6</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>76.67</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -891,7 +915,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -953,7 +977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -985,16 +1009,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920153</v>
+        <v>21330051920176</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1008,16 +1032,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920164</v>
+        <v>20330051920069</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1031,22 +1055,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920176</v>
+        <v>21330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1054,16 +1078,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920069</v>
+        <v>21330051920153</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1072,12 +1096,12 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920253</v>
+        <v>21330051920164</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1086,44 +1110,44 @@
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920081</v>
+        <v>21330051920165</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920250</v>
+        <v>21330051920253</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -1132,21 +1156,21 @@
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920223</v>
+        <v>21330051920081</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1155,21 +1179,21 @@
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920222</v>
+        <v>21330051920250</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
@@ -1178,7 +1202,7 @@
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1187,67 +1211,67 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920190</v>
+        <v>21330051920223</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920205</v>
+        <v>21330051920222</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920208</v>
+        <v>21330051920205</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1256,7 +1280,53 @@
         <v>12</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920208</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920214</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
   <si>
     <t>Mat</t>
   </si>
@@ -103,9 +103,6 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>PORTILLA</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
@@ -179,9 +173,6 @@
   </si>
   <si>
     <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>HARUMI</t>
   </si>
   <si>
     <t>YAEL</t>
@@ -789,16 +780,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -932,16 +926,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>90.31999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -977,7 +971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1015,10 +1009,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1038,10 +1032,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1061,10 +1055,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1084,10 +1078,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1107,10 +1101,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1130,10 +1124,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1153,10 +1147,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1176,10 +1170,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1199,10 +1193,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1216,16 +1210,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920223</v>
+        <v>21330051920222</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1239,22 +1233,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920222</v>
+        <v>21330051920205</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1262,16 +1256,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920205</v>
+        <v>21330051920208</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1285,16 +1279,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920208</v>
+        <v>21330051920214</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1303,29 +1297,6 @@
         <v>12</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920214</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,115 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
     <t>PORTILLA</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
     <t>GETSEMANI GUADALUPE</t>
   </si>
   <si>
     <t>YAEL</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
   </si>
 </sst>
 </file>
@@ -591,10 +498,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>6.5</v>
@@ -617,13 +524,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -666,16 +573,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>74.06999999999999</v>
+        <v>92.59</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -731,16 +638,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -757,16 +664,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -809,16 +716,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>74.06999999999999</v>
+        <v>92.59</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -874,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -900,16 +807,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -952,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>92.59</v>
+      </c>
+      <c r="H5">
         <v>7</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>74.06999999999999</v>
-      </c>
-      <c r="H5">
-        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1003,300 +910,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920176</v>
+        <v>21330051920250</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920069</v>
+        <v>21330051920222</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920190</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920153</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920164</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920165</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920253</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920081</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920250</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920222</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920205</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920208</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920214</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -76,22 +76,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
   </si>
 </sst>
 </file>
@@ -790,7 +799,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,7 +825,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -833,13 +842,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>7.9</v>
@@ -859,13 +868,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>92.59</v>
+        <v>85.19</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -878,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -910,47 +919,70 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920250</v>
+        <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920222</v>
+        <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
@@ -799,7 +799,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -825,7 +825,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -851,7 +851,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -877,7 +877,7 @@
         <v>85.19</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,25 +76,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>NUBE</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
     <t>TZOPITL</t>
   </si>
   <si>
     <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -799,7 +790,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -825,7 +816,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -851,7 +842,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>85.19</v>
+        <v>88.89</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -919,16 +910,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920100</v>
+        <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -937,21 +928,21 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330061430023</v>
+        <v>21330051920203</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -960,29 +951,6 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920203</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>
